--- a/docs/效用树分析.xlsx
+++ b/docs/效用树分析.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10315"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/boywu/Desktop/架构作业1/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\dev\MapCollector\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9F61FDB-291D-8741-9DE7-50F0E18D8D19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F214B95-93FC-435F-984E-53EE391A9153}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5700" yWindow="2320" windowWidth="32940" windowHeight="17360" xr2:uid="{5A0A99F3-840C-FF41-A81D-F2CC94784045}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{5A0A99F3-840C-FF41-A81D-F2CC94784045}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,22 +20,12 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="40">
   <si>
     <t>地图收藏与评价管理系统</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -105,14 +95,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>静默分析控制</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>低负载下，系统对评注静默分析并更新，用户发生高频请求后，系统在0.2s内终止分析进程</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>管理员可以在开发者指导下5分钟内学会对用户、地图、评注的管理和分析</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -194,6 +176,14 @@
   </si>
   <si>
     <t>未来希望集成地图和聊天系统，要在7人日内完成测试并发布</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>多端使用</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>用户能在多端进行使用，保持数据同步</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -201,7 +191,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -240,7 +230,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -252,6 +242,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -568,23 +561,23 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0861067F-5B88-F342-8F86-D20AE4382356}">
   <dimension ref="A1:E14"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
+  <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.83203125" customWidth="1"/>
-    <col min="2" max="2" width="18.6640625" customWidth="1"/>
-    <col min="3" max="3" width="92.6640625" customWidth="1"/>
+    <col min="1" max="1" width="11.81640625" customWidth="1"/>
+    <col min="2" max="2" width="18.6328125" customWidth="1"/>
+    <col min="3" max="3" width="92.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-    </row>
-    <row r="2" spans="1:5">
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -601,7 +594,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>5</v>
       </c>
@@ -618,77 +611,73 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
-      <c r="A4" s="2"/>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="4" t="s">
+        <v>6</v>
+      </c>
       <c r="B4" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" t="s">
         <v>17</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D4" s="1" t="s">
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="4"/>
+      <c r="B5" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E4" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" s="1" t="s">
+      <c r="E5" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="4"/>
+      <c r="B6" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C6" t="s">
+        <v>39</v>
+      </c>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="4"/>
+      <c r="B7" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C7" t="s">
         <v>21</v>
       </c>
-      <c r="C5" t="s">
-        <v>19</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="A6" s="2"/>
-      <c r="B6" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="C6" t="s">
-        <v>25</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="A7" s="2"/>
-      <c r="B7" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C7" t="s">
-        <v>23</v>
-      </c>
       <c r="D7" s="1" t="s">
         <v>15</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C8" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>15</v>
@@ -697,15 +686,15 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="15" customHeight="1">
-      <c r="A9" s="2" t="s">
+    <row r="9" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="4" t="s">
         <v>10</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C9" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>16</v>
@@ -714,45 +703,45 @@
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="15" customHeight="1">
-      <c r="A10" s="2"/>
+    <row r="10" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="4"/>
       <c r="B10" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C10" t="s">
+        <v>29</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B11" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C11" t="s">
         <v>31</v>
       </c>
-      <c r="D10" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
-      <c r="A11" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B11" s="1" t="s">
+      <c r="D11" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A12" s="4"/>
+      <c r="B12" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C12" t="s">
         <v>33</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5">
-      <c r="A12" s="1"/>
-      <c r="B12" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="C12" t="s">
-        <v>35</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>16</v>
@@ -761,15 +750,15 @@
         <v>15</v>
       </c>
     </row>
-    <row r="13" spans="1:5">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C13" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>16</v>
@@ -778,15 +767,15 @@
         <v>15</v>
       </c>
     </row>
-    <row r="14" spans="1:5">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C14" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>15</v>
@@ -798,9 +787,9 @@
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="A5:A7"/>
+    <mergeCell ref="A4:A7"/>
     <mergeCell ref="A9:A10"/>
+    <mergeCell ref="A11:A12"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
